--- a/BeatnotePostHotCell/Jun15,2026/Fit_ResultJun15.xlsx
+++ b/BeatnotePostHotCell/Jun15,2026/Fit_ResultJun15.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\Jun15,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jun15,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D709D487-D92F-4412-94A3-0D252CB55B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A3B46F-3669-4CE0-B900-4401AC4021C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="42">
   <si>
     <t>Date</t>
   </si>
@@ -165,16 +165,13 @@
   </si>
   <si>
     <t>Jun15,2026+4-59-36PM</t>
-  </si>
-  <si>
-    <t>Jun15,2026+1-58-55PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,9 +543,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,7 +580,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -608,7 +605,7 @@
       <c r="H2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -633,7 +630,7 @@
       <c r="H3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -658,7 +655,7 @@
       <c r="H4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -683,7 +680,7 @@
       <c r="H5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -708,7 +705,7 @@
       <c r="H6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -733,7 +730,7 @@
       <c r="H7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -758,7 +755,7 @@
       <c r="H8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -783,7 +780,7 @@
       <c r="H9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -808,7 +805,7 @@
       <c r="H10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -833,7 +830,7 @@
       <c r="H11" s="1"/>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -858,7 +855,7 @@
       <c r="H12" s="1"/>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -883,7 +880,7 @@
       <c r="H13" s="1"/>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -908,7 +905,7 @@
       <c r="H14" s="1"/>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -933,7 +930,7 @@
       <c r="H15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -958,7 +955,7 @@
       <c r="H16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -982,7 +979,7 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -1006,7 +1003,7 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -1030,7 +1027,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="42.75">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -1054,7 +1051,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="42.75">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -1078,7 +1075,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="42.75">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -1101,7 +1098,7 @@
         <v>3.6364708689849302E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="42.75">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -1124,7 +1121,7 @@
         <v>2.8920200739009001E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="42.75">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -1147,7 +1144,7 @@
         <v>2.2947181704657499E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="42.75">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -1170,7 +1167,7 @@
         <v>3.5344410523030501E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="42.75">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -1193,7 +1190,7 @@
         <v>3.3983841629788799E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="42.75">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -1216,7 +1213,7 @@
         <v>3.38162753208091E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="42.75">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
@@ -1239,7 +1236,7 @@
         <v>2.6948370741979701E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="42.75">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -1262,7 +1259,7 @@
         <v>2.2873004957014798E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="42.75">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -1285,7 +1282,7 @@
         <v>2.2873004957153502E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="42.75">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -1308,7 +1305,7 @@
         <v>2.2873004957014E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="42.75">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
@@ -1331,7 +1328,7 @@
         <v>2.2873004957572598E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1347,10 +1344,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
-  <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:T44"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1386,12 +1383,12 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="1">
-        <v>0.26064960163891099</v>
+        <v>0.20299557534608501</v>
       </c>
       <c r="C2" s="1">
         <v>1.5328648223324699</v>
@@ -1403,21 +1400,21 @@
         <v>-1.13269358223719E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>3.7254554302048799</v>
+        <v>3.6643019976674802</v>
       </c>
       <c r="G2" s="1">
-        <v>41.643326181046803</v>
+        <v>41.643247909909803</v>
       </c>
       <c r="H2" s="1">
-        <v>1.1567959988173599E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1546792524076599E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="1">
-        <v>0.25338188968269398</v>
+        <v>0.19731634658855901</v>
       </c>
       <c r="C3" s="1">
         <v>1.5325762315687601</v>
@@ -1429,21 +1426,21 @@
         <v>-2.4961065897679998E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>3.6874436273746301</v>
+        <v>3.6262484863739002</v>
       </c>
       <c r="G3" s="1">
-        <v>39.660162426746801</v>
+        <v>39.659854492944902</v>
       </c>
       <c r="H3" s="1">
-        <v>6.4375495191069097E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8152860159172597E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="1">
-        <v>0.25038094455952498</v>
+        <v>0.19499427606217101</v>
       </c>
       <c r="C4" s="1">
         <v>1.5331131045165201</v>
@@ -1455,21 +1452,21 @@
         <v>-1.4713313282947699E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>3.4767254490670099</v>
+        <v>3.4155178836144202</v>
       </c>
       <c r="G4" s="1">
-        <v>39.650079445672397</v>
+        <v>39.649840540202497</v>
       </c>
       <c r="H4" s="1">
-        <v>5.8120625523532497E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693431708304E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="1">
-        <v>0.256215228918099</v>
+        <v>0.19929121653023299</v>
       </c>
       <c r="C5" s="1">
         <v>1.5324940105671601</v>
@@ -1481,21 +1478,21 @@
         <v>-1.4649688082538499E-4</v>
       </c>
       <c r="F5" s="1">
-        <v>3.4792494412617101</v>
+        <v>3.4180716322854998</v>
       </c>
       <c r="G5" s="1">
-        <v>41.675778050529502</v>
+        <v>40.646989566000698</v>
       </c>
       <c r="H5" s="1">
-        <v>9.5507177051786603E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.1599967655668404E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="1">
-        <v>0.25483329669185101</v>
+        <v>0.19845180139427099</v>
       </c>
       <c r="C6" s="1">
         <v>1.53396766694919</v>
@@ -1507,21 +1504,21 @@
         <v>-1.6036216832798501E-4</v>
       </c>
       <c r="F6" s="1">
-        <v>3.4721699691196899</v>
+        <v>3.4110177921734399</v>
       </c>
       <c r="G6" s="1">
-        <v>39.724309930002399</v>
+        <v>39.724309930056201</v>
       </c>
       <c r="H6" s="1">
-        <v>5.7857693431708998E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693431695597E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="1">
-        <v>0.25854387484878599</v>
+        <v>0.20114408935894201</v>
       </c>
       <c r="C7" s="1">
         <v>1.5346220840060201</v>
@@ -1533,21 +1530,21 @@
         <v>-1.8819482655209601E-4</v>
       </c>
       <c r="F7" s="1">
-        <v>3.4780166851776402</v>
+        <v>3.41682816409253</v>
       </c>
       <c r="G7" s="1">
-        <v>41.338962152110398</v>
+        <v>39.735128830009003</v>
       </c>
       <c r="H7" s="1">
-        <v>5.9402229880098898E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8855000029218898E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="1">
-        <v>0.25519336396030601</v>
+        <v>0.198751656579995</v>
       </c>
       <c r="C8" s="1">
         <v>1.53566688361473</v>
@@ -1559,21 +1556,21 @@
         <v>-1.06426607812294E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>3.7267649679667998</v>
+        <v>3.6655588662462399</v>
       </c>
       <c r="G8" s="1">
-        <v>41.736978795548403</v>
+        <v>41.747996291939302</v>
       </c>
       <c r="H8" s="1">
-        <v>1.1570767821160201E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.15710233262069E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1">
-        <v>0.25663303680948102</v>
+        <v>0.19986305957069</v>
       </c>
       <c r="C9" s="1">
         <v>1.53377174040112</v>
@@ -1585,21 +1582,21 @@
         <v>-1.72322171405127E-4</v>
       </c>
       <c r="F9" s="1">
-        <v>3.7293854269711701</v>
+        <v>3.6682085702620602</v>
       </c>
       <c r="G9" s="1">
-        <v>39.823979426771302</v>
+        <v>39.810490215675301</v>
       </c>
       <c r="H9" s="1">
-        <v>6.1385016804782597E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.0423747657981097E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="1">
-        <v>0.25601459599486398</v>
+        <v>0.19941466362585</v>
       </c>
       <c r="C10" s="1">
         <v>1.5358679740365</v>
@@ -1611,21 +1608,21 @@
         <v>-1.5959564927840099E-4</v>
       </c>
       <c r="F10" s="1">
-        <v>3.7301552277880199</v>
+        <v>3.6689612107596399</v>
       </c>
       <c r="G10" s="1">
-        <v>39.8014930077549</v>
+        <v>39.930527978064497</v>
       </c>
       <c r="H10" s="1">
-        <v>6.1133121933704701E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.4236996068068697E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="1">
-        <v>0.25648553124648299</v>
+        <v>0.19974551641855301</v>
       </c>
       <c r="C11" s="1">
         <v>1.53460907106027</v>
@@ -1637,21 +1634,21 @@
         <v>-1.84491339744843E-4</v>
       </c>
       <c r="F11" s="1">
-        <v>3.7266714239369998</v>
+        <v>3.6655119298122401</v>
       </c>
       <c r="G11" s="1">
-        <v>39.860985722667401</v>
+        <v>39.834761033065902</v>
       </c>
       <c r="H11" s="1">
-        <v>5.8026715025716595E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7915923454981695E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="1">
-        <v>0.25339182435774998</v>
+        <v>0.19734425148693999</v>
       </c>
       <c r="C12" s="1">
         <v>1.5344716795183999</v>
@@ -1663,21 +1660,21 @@
         <v>-1.6850117757017701E-4</v>
       </c>
       <c r="F12" s="1">
-        <v>3.7236660185934198</v>
+        <v>3.6624704973739801</v>
       </c>
       <c r="G12" s="1">
-        <v>39.845865591504101</v>
+        <v>39.8418670058619</v>
       </c>
       <c r="H12" s="1">
-        <v>5.8080340957527101E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8268065912341104E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="1">
-        <v>0.26261256236820102</v>
+        <v>0.20451746200448701</v>
       </c>
       <c r="C13" s="1">
         <v>1.53309472608373</v>
@@ -1689,21 +1686,21 @@
         <v>-2.6350232311559899E-4</v>
       </c>
       <c r="F13" s="1">
-        <v>3.72617703403776</v>
+        <v>3.6650280530497601</v>
       </c>
       <c r="G13" s="1">
-        <v>41.843335189963703</v>
+        <v>41.841672725061997</v>
       </c>
       <c r="H13" s="1">
-        <v>1.15715386860953E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.13792680856548E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="1">
-        <v>0.25914013258546797</v>
+        <v>0.20186014691704701</v>
       </c>
       <c r="C14" s="1">
         <v>1.5372232915827899</v>
@@ -1715,21 +1712,21 @@
         <v>-1.7252086624610201E-4</v>
       </c>
       <c r="F14" s="1">
-        <v>2.4397006774594199</v>
+        <v>2.3785407229825801</v>
       </c>
       <c r="G14" s="1">
-        <v>41.882551372600801</v>
+        <v>41.8829872513477</v>
       </c>
       <c r="H14" s="1">
-        <v>1.0389221125219001E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1571512453511801E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="1">
-        <v>0.25187380012057398</v>
+        <v>0.19616147617243301</v>
       </c>
       <c r="C15" s="1">
         <v>1.5322874450635</v>
@@ -1741,21 +1738,21 @@
         <v>-2.4434144565784897E-4</v>
       </c>
       <c r="F15" s="1">
-        <v>3.7327299129321401</v>
+        <v>3.6715264329371098</v>
       </c>
       <c r="G15" s="1">
-        <v>39.870500681713899</v>
+        <v>39.870584665821298</v>
       </c>
       <c r="H15" s="1">
-        <v>5.7949602435014797E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7968920473327904E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="1">
-        <v>0.25861462842520899</v>
+        <v>0.20141708222610599</v>
       </c>
       <c r="C16" s="1">
         <v>1.53369612235063</v>
@@ -1767,21 +1764,21 @@
         <v>-2.8769265408457202E-4</v>
       </c>
       <c r="F16" s="1">
-        <v>3.71639990906715</v>
+        <v>3.65521373769807</v>
       </c>
       <c r="G16" s="1">
-        <v>41.904197130962103</v>
+        <v>41.904495412673299</v>
       </c>
       <c r="H16" s="1">
-        <v>1.1434915051637201E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.15715014797924E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="1">
-        <v>0.26412000142144099</v>
+        <v>0.20570646230981299</v>
       </c>
       <c r="C17" s="1">
         <v>1.53667099434763</v>
@@ -1793,472 +1790,416 @@
         <v>-3.36052586663455E-4</v>
       </c>
       <c r="F17" s="1">
-        <v>2.7264269779936599</v>
+        <v>2.6652488946657602</v>
       </c>
       <c r="G17" s="1">
-        <v>41.924929079972998</v>
+        <v>41.9249290799984</v>
       </c>
       <c r="H17" s="1">
-        <v>1.15715386862544E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.15715386858856E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.198433606499996</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1.53703721077572</v>
+      </c>
+      <c r="D18" s="1">
+        <v>8.9030775716636196E-4</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-1.91612780406248E-4</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2.1662246452276799</v>
+      </c>
+      <c r="G18" s="1">
+        <v>39.912203147479197</v>
+      </c>
+      <c r="H18" s="1">
+        <v>6.2684121929558402E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="42.75">
+      <c r="A19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.19684836052329399</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1.53682687135992</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1.0306078163870699E-3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>-1.5052661503212999E-4</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2.1660148890812798</v>
+      </c>
+      <c r="G19" s="1">
+        <v>39.9208257108439</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5.98957183416692E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="42.75">
+      <c r="A20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.19797213592714</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.53797097006437</v>
+      </c>
+      <c r="D20" s="1">
+        <v>7.8857199206795899E-4</v>
+      </c>
+      <c r="E20" s="1">
+        <v>-1.11096886899533E-4</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1.91620242568738</v>
+      </c>
+      <c r="G20" s="1">
+        <v>39.9380618151989</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5.7857711397154502E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="42.75">
+      <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="1">
-        <v>0.25355249186689299</v>
-      </c>
-      <c r="C18" s="1">
+      <c r="B21" s="1">
+        <v>0.19746160960659001</v>
+      </c>
+      <c r="C21" s="1">
         <v>1.5377912888207299</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D21" s="1">
         <v>1.0315597785770299E-3</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E21" s="1">
         <v>-1.5617765394321801E-4</v>
       </c>
-      <c r="F18" s="1">
-        <v>2.2257689325990202</v>
-      </c>
-      <c r="G18" s="1">
-        <v>39.942100280494401</v>
-      </c>
-      <c r="H18" s="1">
-        <v>5.7857693460583795E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+      <c r="F21" s="1">
+        <v>2.16459409094068</v>
+      </c>
+      <c r="G21" s="1">
+        <v>39.942100280001</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5.7857693436110002E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="42.75">
+      <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1">
-        <v>0.258640908855092</v>
-      </c>
-      <c r="C19" s="1">
+      <c r="B22" s="1">
+        <v>0.201235306306627</v>
+      </c>
+      <c r="C22" s="1">
         <v>1.5385355536295999</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D22" s="1">
         <v>1.0545236320853399E-3</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E22" s="1">
         <v>-1.6652063188563201E-4</v>
       </c>
-      <c r="F19" s="1">
-        <v>1.9765134767843899</v>
-      </c>
-      <c r="G19" s="1">
-        <v>41.982256063640598</v>
-      </c>
-      <c r="H19" s="1">
-        <v>8.3428955916662402E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+      <c r="F22" s="1">
+        <v>1.9153349314619901</v>
+      </c>
+      <c r="G22" s="1">
+        <v>41.072924313030398</v>
+      </c>
+      <c r="H22" s="1">
+        <v>6.1130145336541104E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="42.75">
+      <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="1">
-        <v>0.25176887581155899</v>
-      </c>
-      <c r="C20" s="1">
+      <c r="B23" s="1">
+        <v>0.19609449317179301</v>
+      </c>
+      <c r="C23" s="1">
         <v>1.54050077260495</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D23" s="1">
         <v>9.2736795036745998E-4</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E23" s="1">
         <v>-1.18749717131734E-4</v>
       </c>
-      <c r="F20" s="1">
-        <v>2.23048138826569</v>
-      </c>
-      <c r="G20" s="1">
-        <v>40.000909460223298</v>
-      </c>
-      <c r="H20" s="1">
-        <v>5.7857694052745998E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+      <c r="F23" s="1">
+        <v>2.1693236689642998</v>
+      </c>
+      <c r="G23" s="1">
+        <v>40.002655441238097</v>
+      </c>
+      <c r="H23" s="1">
+        <v>6.4235271668997202E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="42.75">
+      <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="1">
-        <v>0.25436276153236997</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="B24" s="1">
+        <v>0.198095518321387</v>
+      </c>
+      <c r="C24" s="1">
         <v>1.5396693456839099</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D24" s="1">
         <v>2.0421799979558801E-3</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E24" s="1">
         <v>-2.9987791974024001E-4</v>
       </c>
-      <c r="F21" s="1">
-        <v>2.4732130482346499</v>
-      </c>
-      <c r="G21" s="1">
-        <v>40.012278822183802</v>
-      </c>
-      <c r="H21" s="1">
-        <v>5.8587026377106798E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.248026860502817</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1.5409074136751699</v>
-      </c>
-      <c r="D22" s="1">
-        <v>9.2702370388084805E-4</v>
-      </c>
-      <c r="E22" s="1">
-        <v>-1.3108115361235701E-4</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1.9780003717511201</v>
-      </c>
-      <c r="G22" s="1">
-        <v>40.0221381497321</v>
-      </c>
-      <c r="H22" s="1">
-        <v>5.7857693918081203E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.25505739125523702</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1.53703721077572</v>
-      </c>
-      <c r="D23" s="1">
-        <v>8.9030775716636196E-4</v>
-      </c>
-      <c r="E23" s="1">
-        <v>-1.91612780406248E-4</v>
-      </c>
-      <c r="F23" s="1">
-        <v>2.22739003656485</v>
-      </c>
-      <c r="G23" s="1">
-        <v>40.120664268270701</v>
-      </c>
-      <c r="H23" s="1">
-        <v>1.1570594106726001E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.25268334549192301</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1.5369398473239</v>
-      </c>
-      <c r="D24" s="1">
-        <v>8.8276360040418997E-4</v>
-      </c>
-      <c r="E24" s="1">
-        <v>-1.2193057223206699E-4</v>
-      </c>
       <c r="F24" s="1">
-        <v>2.2272137240521599</v>
+        <v>2.4120291075526699</v>
       </c>
       <c r="G24" s="1">
-        <v>39.915182061183202</v>
+        <v>40.012278840144198</v>
       </c>
       <c r="H24" s="1">
-        <v>5.7858379915798905E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693432276198E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="42.75">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1">
-        <v>0.254203134019032</v>
+        <v>0.201202131188608</v>
       </c>
       <c r="C25" s="1">
-        <v>1.53797097006437</v>
+        <v>1.54071283209849</v>
       </c>
       <c r="D25" s="1">
-        <v>7.8857199206795899E-4</v>
+        <v>1.02838840321871E-3</v>
       </c>
       <c r="E25" s="1">
-        <v>-1.11096886899533E-4</v>
+        <v>-1.4108550411155699E-4</v>
       </c>
       <c r="F25" s="1">
-        <v>1.9773947120765001</v>
+        <v>1.9136411567612199</v>
       </c>
       <c r="G25" s="1">
-        <v>39.9384385042611</v>
+        <v>40.145154929747399</v>
       </c>
       <c r="H25" s="1">
-        <v>5.8049458530124104E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.9238149706494399E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="42.75">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1">
-        <v>0.25848980394328103</v>
+        <v>0.19854017174952801</v>
       </c>
       <c r="C26" s="1">
-        <v>1.54071283209849</v>
+        <v>1.54065616468318</v>
       </c>
       <c r="D26" s="1">
-        <v>1.02838840321871E-3</v>
+        <v>1.07253335140665E-3</v>
       </c>
       <c r="E26" s="1">
-        <v>-1.4108550411155699E-4</v>
+        <v>-1.60382971276615E-4</v>
       </c>
       <c r="F26" s="1">
-        <v>1.9748178444790301</v>
+        <v>1.9176605052327</v>
       </c>
       <c r="G26" s="1">
-        <v>41.080889229405003</v>
+        <v>40.084837720003698</v>
       </c>
       <c r="H26" s="1">
-        <v>7.5215880885330698E-4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693434489401E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="42.75">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1">
-        <v>0.25493042534243598</v>
+        <v>0.20017070885951799</v>
       </c>
       <c r="C27" s="1">
-        <v>1.54065616468318</v>
+        <v>1.5404036386186599</v>
       </c>
       <c r="D27" s="1">
-        <v>1.07253335140665E-3</v>
+        <v>1.10705073013245E-3</v>
       </c>
       <c r="E27" s="1">
-        <v>-1.60382971276615E-4</v>
+        <v>-1.5193379721210599E-4</v>
       </c>
       <c r="F27" s="1">
-        <v>1.9788524330411501</v>
+        <v>1.9280476320878801</v>
       </c>
       <c r="G27" s="1">
-        <v>40.084838224482802</v>
+        <v>42.012169051090801</v>
       </c>
       <c r="H27" s="1">
-        <v>5.7902274992843001E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1531671710992601E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="42.75">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1">
-        <v>0.25702073078272197</v>
+        <v>0.19706209535145</v>
       </c>
       <c r="C28" s="1">
-        <v>1.5404036386186599</v>
+        <v>1.5410019101857999</v>
       </c>
       <c r="D28" s="1">
-        <v>1.10705073013245E-3</v>
+        <v>8.7650443534686203E-4</v>
       </c>
       <c r="E28" s="1">
-        <v>-1.5193379721210599E-4</v>
+        <v>-1.19154075123252E-4</v>
       </c>
       <c r="F28" s="1">
-        <v>1.98923182065068</v>
+        <v>1.6737394929261999</v>
       </c>
       <c r="G28" s="1">
-        <v>42.041990931149499</v>
+        <v>40.126663572756698</v>
       </c>
       <c r="H28" s="1">
-        <v>1.1430026774338199E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.11292458919408E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="42.75">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1">
-        <v>0.25281370286486299</v>
+        <v>0.200682963445732</v>
       </c>
       <c r="C29" s="1">
-        <v>1.5410019101857999</v>
+        <v>1.5389962904085099</v>
       </c>
       <c r="D29" s="1">
-        <v>8.7650443534686203E-4</v>
+        <v>1.0686995005526E-3</v>
       </c>
       <c r="E29" s="1">
-        <v>-1.19154075123252E-4</v>
+        <v>-1.49314408589812E-4</v>
       </c>
       <c r="F29" s="1">
-        <v>1.7349154450425199</v>
+        <v>1.87793098402192</v>
       </c>
       <c r="G29" s="1">
-        <v>40.126889689282699</v>
+        <v>42.1306966499194</v>
       </c>
       <c r="H29" s="1">
-        <v>5.9960864702691995E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.9504625956987704E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="42.75">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1">
-        <v>0.25787828139437702</v>
+        <v>0.19843356572069301</v>
       </c>
       <c r="C30" s="1">
-        <v>1.5389962904085099</v>
+        <v>1.53965330946838</v>
       </c>
       <c r="D30" s="1">
-        <v>1.0686995005526E-3</v>
+        <v>9.6885811848044297E-4</v>
       </c>
       <c r="E30" s="1">
-        <v>-1.49314408589812E-4</v>
+        <v>-1.20798063154706E-4</v>
       </c>
       <c r="F30" s="1">
-        <v>1.9390792578303599</v>
+        <v>1.9181781030656999</v>
       </c>
       <c r="G30" s="1">
-        <v>42.132881227502999</v>
+        <v>40.157384424517403</v>
       </c>
       <c r="H30" s="1">
-        <v>1.1449144005288899E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8304272458532E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="42.75">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1">
-        <v>0.255030114263046</v>
+        <v>0.19746491101406</v>
       </c>
       <c r="C31" s="1">
-        <v>1.53965330946838</v>
+        <v>1.5396800422580701</v>
       </c>
       <c r="D31" s="1">
-        <v>9.6885811848044297E-4</v>
-      </c>
-      <c r="E31" s="1">
-        <v>-1.20798063154706E-4</v>
+        <v>7.7184519752308996E-4</v>
+      </c>
+      <c r="E31" s="2">
+        <v>-5.9195175119446801E-5</v>
       </c>
       <c r="F31" s="1">
-        <v>1.97936333720181</v>
+        <v>1.66462072229951</v>
       </c>
       <c r="G31" s="1">
-        <v>41.148559168543301</v>
+        <v>41.812213882419101</v>
       </c>
       <c r="H31" s="1">
-        <v>7.5215877457013097E-4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1564519884125399E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="42.75">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="1">
-        <v>0.25326708245889501</v>
+        <v>0.201690348999186</v>
       </c>
       <c r="C32" s="1">
-        <v>1.5396800422580701</v>
+        <v>1.5388815259605999</v>
       </c>
       <c r="D32" s="1">
-        <v>7.7184519752308996E-4</v>
-      </c>
-      <c r="E32" s="2">
-        <v>-5.9195175119446801E-5</v>
+        <v>1.25729050302833E-3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>-1.7376737329282999E-4</v>
       </c>
       <c r="F32" s="1">
-        <v>1.72577858428638</v>
+        <v>2.1604332296322499</v>
       </c>
       <c r="G32" s="1">
-        <v>41.160489583464297</v>
+        <v>42.193520033336199</v>
       </c>
       <c r="H32" s="1">
-        <v>7.5215937064753704E-4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.25901851572451601</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1.5388815259605999</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1.25729050302833E-3</v>
-      </c>
-      <c r="E33" s="1">
-        <v>-1.7376737329282999E-4</v>
-      </c>
-      <c r="F33" s="1">
-        <v>2.2215774386157299</v>
-      </c>
-      <c r="G33" s="1">
-        <v>42.186764481886101</v>
-      </c>
-      <c r="H33" s="1">
-        <v>1.15179674848183E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1.056585509583E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="2"/>
+      <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2268,7 +2209,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2278,15 +2219,55 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="2"/>
+      <c r="D40" s="1"/>
       <c r="E40" s="2"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2295,13 +2276,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="5" max="5" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2312,7 +2293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -2320,7 +2301,7 @@
         <v>15.5831740366148</v>
       </c>
       <c r="C2" s="1">
-        <v>0.26064960163891099</v>
+        <v>0.20299557534608501</v>
       </c>
       <c r="F2">
         <v>894</v>
@@ -2328,8 +2309,9 @@
       <c r="G2">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -2337,7 +2319,7 @@
         <v>15.6181213588261</v>
       </c>
       <c r="C3" s="1">
-        <v>0.25338188968269398</v>
+        <v>0.19731634658855901</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -2348,10 +2330,11 @@
       </c>
       <c r="G3">
         <f>AVERAGE(C2:C33)</f>
-        <v>0.25602586707212527</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.1993665486863799</v>
+      </c>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -2359,7 +2342,7 @@
         <v>15.471660411280601</v>
       </c>
       <c r="C4" s="1">
-        <v>0.25038094455952498</v>
+        <v>0.19499427606217101</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
@@ -2370,10 +2353,11 @@
       </c>
       <c r="G4">
         <f>_xlfn.STDEV.S(C2:C33)</f>
-        <v>3.2022347175441634E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.4698309486633186E-3</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -2381,7 +2365,7 @@
         <v>15.4286358328345</v>
       </c>
       <c r="C5" s="1">
-        <v>0.256215228918099</v>
+        <v>0.19929121653023299</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -2392,10 +2376,11 @@
       </c>
       <c r="G5">
         <f>G4/G3/SQRT(COUNT(C2:C33))</f>
-        <v>2.246407131366617E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.2250208794433344E-3</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -2403,10 +2388,11 @@
         <v>15.725390191826</v>
       </c>
       <c r="C6" s="1">
-        <v>0.25483329669185101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19845180139427099</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2414,10 +2400,11 @@
         <v>15.6295450777592</v>
       </c>
       <c r="C7" s="1">
-        <v>0.25854387484878599</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20114408935894201</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -2425,10 +2412,11 @@
         <v>15.5447105698267</v>
       </c>
       <c r="C8" s="1">
-        <v>0.25519336396030601</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.198751656579995</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -2436,10 +2424,11 @@
         <v>15.641779033917301</v>
       </c>
       <c r="C9" s="1">
-        <v>0.25663303680948102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19986305957069</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -2447,10 +2436,11 @@
         <v>15.560241393406899</v>
       </c>
       <c r="C10" s="1">
-        <v>0.25601459599486398</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19941466362585</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -2458,10 +2448,11 @@
         <v>15.6798903930978</v>
       </c>
       <c r="C11" s="1">
-        <v>0.25648553124648299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19974551641855301</v>
+      </c>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -2469,10 +2460,11 @@
         <v>15.5257705053734</v>
       </c>
       <c r="C12" s="1">
-        <v>0.25339182435774998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19734425148693999</v>
+      </c>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -2480,10 +2472,11 @@
         <v>15.5068553708303</v>
       </c>
       <c r="C13" s="1">
-        <v>0.26261256236820102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20451746200448701</v>
+      </c>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -2491,10 +2484,11 @@
         <v>15.7245514226287</v>
       </c>
       <c r="C14" s="1">
-        <v>0.25914013258546797</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20186014691704701</v>
+      </c>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,10 +2496,11 @@
         <v>15.653971830187899</v>
       </c>
       <c r="C15" s="1">
-        <v>0.25187380012057398</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19616147617243301</v>
+      </c>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -2513,10 +2508,11 @@
         <v>15.585241971938</v>
       </c>
       <c r="C16" s="1">
-        <v>0.25861462842520899</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20141708222610599</v>
+      </c>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -2524,10 +2520,11 @@
         <v>15.591441713773801</v>
       </c>
       <c r="C17" s="1">
-        <v>0.26412000142144099</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20570646230981299</v>
+      </c>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -2535,10 +2532,11 @@
         <v>15.513624662526899</v>
       </c>
       <c r="C18" s="1">
-        <v>0.25505739125523702</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.198433606499996</v>
+      </c>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,10 +2544,11 @@
         <v>15.550450799138201</v>
       </c>
       <c r="C19" s="1">
-        <v>0.25268334549192301</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19684836052329399</v>
+      </c>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" ht="42.75">
       <c r="A20" s="1" t="s">
         <v>33</v>
       </c>
@@ -2557,10 +2556,11 @@
         <v>15.5999990421973</v>
       </c>
       <c r="C20" s="1">
-        <v>0.254203134019032</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19797213592714</v>
+      </c>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" ht="42.75">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -2568,10 +2568,11 @@
         <v>15.5612294230614</v>
       </c>
       <c r="C21" s="1">
-        <v>0.25355249186689299</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19746160960659001</v>
+      </c>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" ht="42.75">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -2579,10 +2580,11 @@
         <v>15.389959627991299</v>
       </c>
       <c r="C22" s="1">
-        <v>0.258640908855092</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.201235306306627</v>
+      </c>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" ht="42.75">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -2590,10 +2592,11 @@
         <v>15.6769168147221</v>
       </c>
       <c r="C23" s="1">
-        <v>0.25176887581155899</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19609449317179301</v>
+      </c>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" ht="42.75">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -2601,10 +2604,11 @@
         <v>15.516217850365001</v>
       </c>
       <c r="C24" s="1">
-        <v>0.25436276153236997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.198095518321387</v>
+      </c>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" ht="42.75">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -2612,10 +2616,11 @@
         <v>15.4712021433598</v>
       </c>
       <c r="C25" s="1">
-        <v>0.25848980394328103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.201202131188608</v>
+      </c>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" ht="42.75">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -2623,10 +2628,11 @@
         <v>15.4267437621642</v>
       </c>
       <c r="C26" s="1">
-        <v>0.25493042534243598</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19854017174952801</v>
+      </c>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" ht="42.75">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -2634,10 +2640,11 @@
         <v>15.363023447442201</v>
       </c>
       <c r="C27" s="1">
-        <v>0.25702073078272197</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.20017070885951799</v>
+      </c>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" ht="42.75">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
@@ -2645,10 +2652,11 @@
         <v>15.4784018893041</v>
       </c>
       <c r="C28" s="1">
-        <v>0.25281370286486299</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19706209535145</v>
+      </c>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" ht="42.75">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -2656,10 +2664,11 @@
         <v>15.598700910453401</v>
       </c>
       <c r="C29" s="1">
-        <v>0.25787828139437702</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.200682963445732</v>
+      </c>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" ht="42.75">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -2667,10 +2676,11 @@
         <v>15.699463941581101</v>
       </c>
       <c r="C30" s="1">
-        <v>0.255030114263046</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19843356572069301</v>
+      </c>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" ht="42.75">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -2678,10 +2688,11 @@
         <v>15.751226314712399</v>
       </c>
       <c r="C31" s="1">
-        <v>0.25326708245889501</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.19746491101406</v>
+      </c>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" ht="42.75">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
@@ -2689,30 +2700,31 @@
         <v>15.601321813860199</v>
       </c>
       <c r="C32" s="1">
-        <v>0.25901851572451601</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>0.201690348999186</v>
+      </c>
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3">
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3">
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3">
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3">
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3">
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3">
       <c r="C39" s="1"/>
     </row>
   </sheetData>
